--- a/docs/RECL_Employee_Import.xlsx
+++ b/docs/RECL_Employee_Import.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kinsh.000\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hrms\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5169B7F-5EA6-4129-8250-CB4BB466A609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -1780,7 +1779,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2157,18 +2156,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="9" max="9" width="26.28515625" customWidth="1"/>
-    <col min="21" max="21" width="17.28515625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" customWidth="1"/>
+    <col min="7" max="7" width="32.453125" customWidth="1"/>
+    <col min="8" max="8" width="29.453125" customWidth="1"/>
+    <col min="9" max="9" width="26.26953125" customWidth="1"/>
+    <col min="21" max="21" width="17.26953125" style="5" customWidth="1"/>
     <col min="22" max="22" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="21.7265625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2254,7 +2255,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -2310,7 +2311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2366,7 +2367,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -2419,7 +2420,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2481,7 +2482,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2540,7 +2541,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2670,7 +2671,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2726,7 +2727,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -2791,7 +2792,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2847,7 +2848,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2903,7 +2904,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -3030,7 +3031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3092,7 +3093,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -3154,7 +3155,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -3219,7 +3220,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -3284,7 +3285,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -3349,7 +3350,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3414,7 +3415,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3479,7 +3480,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -3544,7 +3545,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -3665,7 +3666,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -3730,7 +3731,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -3854,7 +3855,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -3919,7 +3920,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3984,7 +3985,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -4049,7 +4050,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -4102,7 +4103,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -4167,7 +4168,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -4232,7 +4233,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -4294,7 +4295,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -4356,7 +4357,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -4418,7 +4419,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -4471,7 +4472,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -4533,7 +4534,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -4595,7 +4596,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -4660,7 +4661,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -4725,7 +4726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>28</v>
       </c>
@@ -4790,7 +4791,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -4855,7 +4856,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>28</v>
       </c>
@@ -4920,7 +4921,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -4982,7 +4983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>28</v>
       </c>
@@ -5044,7 +5045,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -5106,7 +5107,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -5168,7 +5169,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -5230,7 +5231,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>28</v>
       </c>
@@ -5292,7 +5293,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>28</v>
       </c>
@@ -5354,7 +5355,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>28</v>
       </c>
@@ -5410,7 +5411,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>28</v>
       </c>
@@ -5469,7 +5470,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>28</v>
       </c>
@@ -5528,7 +5529,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>28</v>
       </c>
@@ -5587,7 +5588,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -5646,7 +5647,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>28</v>
       </c>
@@ -5705,7 +5706,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>28</v>
       </c>
@@ -5764,7 +5765,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>28</v>
       </c>
@@ -5823,7 +5824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>28</v>
       </c>
@@ -5882,7 +5883,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>28</v>
       </c>
@@ -5941,7 +5942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>28</v>
       </c>
@@ -5997,7 +5998,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -6056,7 +6057,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>28</v>
       </c>
@@ -6115,7 +6116,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -6174,7 +6175,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>28</v>
       </c>
@@ -6233,7 +6234,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>28</v>
       </c>
@@ -6289,7 +6290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>28</v>
       </c>
@@ -6345,7 +6346,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>28</v>
       </c>
@@ -6401,7 +6402,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>28</v>
       </c>
@@ -6457,7 +6458,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -6569,7 +6570,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -6622,7 +6623,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -6678,7 +6679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -6790,7 +6791,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -6846,7 +6847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -6902,7 +6903,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -6958,7 +6959,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -7014,7 +7015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -7070,7 +7071,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -7126,7 +7127,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -7182,7 +7183,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -7238,7 +7239,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>28</v>
       </c>
@@ -7294,7 +7295,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>28</v>
       </c>
@@ -7353,7 +7354,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>28</v>
       </c>
@@ -7412,7 +7413,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>28</v>
       </c>
@@ -7465,7 +7466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>28</v>
       </c>
@@ -7518,7 +7519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>28</v>
       </c>
@@ -7571,7 +7572,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>28</v>
       </c>
@@ -7627,7 +7628,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>28</v>
       </c>
@@ -7683,7 +7684,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>28</v>
       </c>
@@ -7739,7 +7740,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>28</v>
       </c>
@@ -7789,7 +7790,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>28</v>
       </c>
@@ -7844,7 +7845,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{83E004C9-019F-4E05-A669-1D7130309EC1}"/>
+    <hyperlink ref="G8" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
